--- a/448-contenu-fhir---ajout-du-projet-de-vie/ig/ValueSet-tddui-goal-Identifier-projet-vie.xlsx
+++ b/448-contenu-fhir---ajout-du-projet-de-vie/ig/ValueSet-tddui-goal-Identifier-projet-vie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T07:22:25+00:00</t>
+    <t>2026-06-11T14:21:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/448-contenu-fhir---ajout-du-projet-de-vie/ig/ValueSet-tddui-goal-Identifier-projet-vie.xlsx
+++ b/448-contenu-fhir---ajout-du-projet-de-vie/ig/ValueSet-tddui-goal-Identifier-projet-vie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T14:21:35+00:00</t>
+    <t>2026-06-11T15:13:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
